--- a/files/XLOOKUP Excel Tutorial File.xlsx
+++ b/files/XLOOKUP Excel Tutorial File.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/579481080490e445/Documents/Excel Series Excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\advance_excel\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{625F3FEF-17C5-43E2-BFC2-A4868BFCBA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F2D198-F35F-4E66-87CA-F89B2A1F6AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="6" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
   </bookViews>
   <sheets>
     <sheet name="XLookUp" sheetId="1" r:id="rId1"/>
@@ -39,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="91">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -301,9 +323,6 @@
   </si>
   <si>
     <t>Toby Flender</t>
-  </si>
-  <si>
-    <t>Kevin Malo</t>
   </si>
   <si>
     <t>Start Date</t>
@@ -373,9 +392,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -413,7 +432,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -519,7 +538,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -661,7 +680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -672,7 +691,8 @@
   <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -695,7 +715,7 @@
         <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K1" t="s">
         <v>4</v>
@@ -761,6 +781,10 @@
       <c r="A3" t="s">
         <v>65</v>
       </c>
+      <c r="B3" t="str">
+        <f>_xlfn.XLOOKUP(A3,H2:H10,P2:P10)</f>
+        <v>Toby.Flenderson@DunderMifflinCorporate.com</v>
+      </c>
       <c r="E3">
         <v>1002</v>
       </c>
@@ -799,6 +823,10 @@
       <c r="A4" t="s">
         <v>62</v>
       </c>
+      <c r="B4" t="str">
+        <f t="shared" ref="B4:B6" si="0">_xlfn.XLOOKUP(A4,H3:H11,P3:P11)</f>
+        <v>Pam.Beasley@DunderMifflin.com</v>
+      </c>
       <c r="E4">
         <v>1003</v>
       </c>
@@ -837,6 +865,10 @@
       <c r="A5" t="s">
         <v>67</v>
       </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>Meredith.Palmer@Yahoo.com</v>
+      </c>
       <c r="E5">
         <v>1004</v>
       </c>
@@ -875,6 +907,10 @@
       <c r="A6" t="s">
         <v>69</v>
       </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>Kevin.Malone@DunderMifflin.com</v>
+      </c>
       <c r="E6">
         <v>1005</v>
       </c>
@@ -1051,13 +1087,13 @@
     </row>
     <row r="22" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H22" t="str">
-        <f t="shared" ref="H22:H23" si="0">CONCATENATE(F12," ",G12)</f>
+        <f t="shared" ref="H22:H23" si="1">CONCATENATE(F12," ",G12)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="23" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -1072,7 +1108,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -1160,6 +1196,13 @@
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
+      </c>
+      <c r="B3" t="str" cm="1">
+        <f t="array" ref="B3:C3">_xlfn.XLOOKUP(A3,I2:I10,O2:P10)</f>
+        <v>8/30/2017</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Toby.Flenderson@DunderMifflinCorporate.com</v>
       </c>
       <c r="F3">
         <v>1002</v>
@@ -1558,6 +1601,10 @@
       <c r="A3" t="s">
         <v>86</v>
       </c>
+      <c r="B3" t="str" cm="1">
+        <f t="array" ref="B3">_xlfn.XLOOKUP(A3,H2:H10,O2:P10,"Not found")</f>
+        <v>Not found</v>
+      </c>
       <c r="E3">
         <v>1002</v>
       </c>
@@ -1596,6 +1643,10 @@
       <c r="A4" t="s">
         <v>18</v>
       </c>
+      <c r="B4" t="str">
+        <f>_xlfn.XLOOKUP("*"&amp;A4,H3:H11,O3:O11,"Not found",2)</f>
+        <v>Pam.Beasley@DunderMifflin.com</v>
+      </c>
       <c r="E4">
         <v>1003</v>
       </c>
@@ -1632,7 +1683,11 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>67</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" ref="B5:B6" si="0">_xlfn.XLOOKUP(A5,H4:H12,O4:O12,"Not found")</f>
+        <v>Meredith.Palmer@Yahoo.com</v>
       </c>
       <c r="E5">
         <v>1004</v>
@@ -1670,7 +1725,11 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>69</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>Kevin.Malone@DunderMifflin.com</v>
       </c>
       <c r="E6">
         <v>1005</v>
@@ -1848,13 +1907,13 @@
     </row>
     <row r="22" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H22" t="str">
-        <f t="shared" ref="H22:H23" si="0">CONCATENATE(F12," ",G12)</f>
+        <f t="shared" ref="H22:H23" si="1">CONCATENATE(F12," ",G12)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="23" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -1913,10 +1972,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
         <v>88</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
       </c>
       <c r="F2">
         <v>1001</v>
@@ -1954,7 +2013,11 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="B3" t="str">
+        <f>_xlfn.XLOOKUP(A3,N2:N10,I2:I10,,1)</f>
+        <v>Angela Martin</v>
       </c>
       <c r="F3">
         <v>1002</v>
@@ -2308,6 +2371,10 @@
       <c r="A2" t="s">
         <v>70</v>
       </c>
+      <c r="B2">
+        <f>_xlfn.XLOOKUP(I1,H1:S1,H2:S2)</f>
+        <v>310</v>
+      </c>
       <c r="G2" t="s">
         <v>70</v>
       </c>
@@ -2352,6 +2419,10 @@
       <c r="A3" t="s">
         <v>71</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B4" si="0">_xlfn.XLOOKUP(I2,H2:S2,H3:S3)</f>
+        <v>40</v>
+      </c>
       <c r="G3" t="s">
         <v>71</v>
       </c>
@@ -2395,6 +2466,10 @@
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>84</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>118</v>
       </c>
       <c r="G4" t="s">
         <v>84</v>
@@ -2631,6 +2706,10 @@
       <c r="A7" t="s">
         <v>70</v>
       </c>
+      <c r="B7">
+        <f>SUM(_xlfn.XLOOKUP(I1,H1:S1,H2:S2):_xlfn.XLOOKUP(J1,H1:S1,H2:S2))</f>
+        <v>460</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2639,10 +2718,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F9C169-12D8-441E-870D-6C6EF0F6521C}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -2665,7 +2745,7 @@
         <v>4</v>
       </c>
       <c r="K1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L1" t="s">
         <v>5</v>
@@ -2728,6 +2808,10 @@
       <c r="A3" t="s">
         <v>63</v>
       </c>
+      <c r="B3" t="str">
+        <f>VLOOKUP(A3,H2:P10,9,FALSE)</f>
+        <v>Dwight.Schrute@AOL.com</v>
+      </c>
       <c r="E3">
         <v>1002</v>
       </c>
@@ -3011,6 +3095,12 @@
       </c>
       <c r="P10" s="2" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B13" t="str">
+        <f>_xlfn.XLOOKUP(A3,H:H,P:P)</f>
+        <v>Dwight.Schrute@AOL.com</v>
       </c>
     </row>
   </sheetData>
